--- a/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
+++ b/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-10T16:24:07+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
+++ b/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T10:43:11+00:00</t>
+    <t>2025-11-20T10:22:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
+    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
+++ b/publish/ValueSet-NoDomainVitalSignsPulseRhythmIrregularityValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T10:22:37+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>
